--- a/Config/GameConfig/Datas/seasoning.xlsx
+++ b/Config/GameConfig/Datas/seasoning.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Configs\GameConfig\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UnityProject\Framework\Framework\Config\GameConfig\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{065A3C74-E0FF-47F3-AD9A-4201410B70EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7D69F88-74DE-40E1-BB10-B889816EC56D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t>##var</t>
   </si>
@@ -97,9 +97,6 @@
     <t>string</t>
   </si>
   <si>
-    <t>item.EQuality</t>
-  </si>
-  <si>
     <t>##group</t>
   </si>
   <si>
@@ -150,10 +147,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>WHITE</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>普通食盐</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -171,6 +164,10 @@
   </si>
   <si>
     <t>普通糖</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -569,6 +566,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="21.75" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -631,7 +631,7 @@
         <v>8</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>8</v>
@@ -652,13 +652,13 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
@@ -674,22 +674,22 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>16</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>17</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -707,13 +707,13 @@
         <v>1060001</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -724,13 +724,13 @@
         <v>1060002</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="3" t="s">
         <v>19</v>
       </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
       <c r="E7" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -741,13 +741,13 @@
         <v>1060003</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F8">
         <v>5</v>
